--- a/job_application_forms/041_security_employment_application_form--job_application_forms.xlsx
+++ b/job_application_forms/041_security_employment_application_form--job_application_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -738,8 +738,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -767,12 +767,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_10,_'name':_'less_than_1_year',_'label':_'less_than_1_year'}</t>
+          <t>less_than_1_year</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 10, 'name': 'Less than 1 year', 'label': 'Less than 1 year'}</t>
+          <t>Less than 1 year</t>
         </is>
       </c>
     </row>
@@ -784,12 +784,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_11,_'name':_'1-5_years',_'label':_'1-5_years'}</t>
+          <t>1-5_years</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 11, 'name': '1-5 years', 'label': '1-5 years'}</t>
+          <t>1-5 years</t>
         </is>
       </c>
     </row>
@@ -801,12 +801,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_12,_'name':_'5+_years',_'label':_'5+_years'}</t>
+          <t>5+_years</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 12, 'name': '5+ years', 'label': '5+ years'}</t>
+          <t>5+ years</t>
         </is>
       </c>
     </row>
@@ -818,12 +818,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_13,_'name':_'high_school_diploma',_'label':_'high_school_diploma'}</t>
+          <t>high_school_diploma</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 13, 'name': 'High School Diploma', 'label': 'High School Diploma'}</t>
+          <t>High School Diploma</t>
         </is>
       </c>
     </row>
@@ -835,12 +835,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_14,_'name':_"bachelor's_degree",_'label':_"bachelor's_degree"}</t>
+          <t>bachelor's_degree</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 14, 'name': "Bachelor's Degree", 'label': "Bachelor's Degree"}</t>
+          <t>Bachelor's Degree</t>
         </is>
       </c>
     </row>
@@ -852,12 +852,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_15,_'name':_"master's_degree",_'label':_"master's_degree"}</t>
+          <t>master's_degree</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 15, 'name': "Master's Degree", 'label': "Master's Degree"}</t>
+          <t>Master's Degree</t>
         </is>
       </c>
     </row>
@@ -869,12 +869,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_16,_'name':_'other',_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 16, 'name': 'Other', 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -886,12 +886,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_17,_'name':_'unemployed',_'label':_'unemployed'}</t>
+          <t>unemployed</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 17, 'name': 'Unemployed', 'label': 'Unemployed'}</t>
+          <t>Unemployed</t>
         </is>
       </c>
     </row>
@@ -903,12 +903,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_18,_'name':_'employed',_'label':_'employed'}</t>
+          <t>employed</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 18, 'name': 'Employed', 'label': 'Employed'}</t>
+          <t>Employed</t>
         </is>
       </c>
     </row>
@@ -920,12 +920,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_19,_'name':_'retired',_'label':_'retired'}</t>
+          <t>retired</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 19, 'name': 'Retired', 'label': 'Retired'}</t>
+          <t>Retired</t>
         </is>
       </c>
     </row>
@@ -937,12 +937,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_20,_'name':_'other',_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 20, 'name': 'Other', 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
